--- a/artfynd/A 3930-2026 artfynd.xlsx
+++ b/artfynd/A 3930-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73025440</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585763.224404155</v>
+        <v>585763</v>
       </c>
       <c r="R2" t="n">
-        <v>6668999.920794568</v>
+        <v>6669000</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73025446</v>
+        <v>73025451</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,7 +816,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585977.0883084256</v>
+        <v>586071</v>
       </c>
       <c r="R3" t="n">
-        <v>6669178.781244222</v>
+        <v>6669285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,26 +858,16 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73025441</v>
+        <v>73025446</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,27 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585750.8283202611</v>
+        <v>585977</v>
       </c>
       <c r="R4" t="n">
-        <v>6668975.221210712</v>
+        <v>6669179</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,26 +964,16 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1034,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73025445</v>
+        <v>73025439</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585943.0612866395</v>
+        <v>586126</v>
       </c>
       <c r="R5" t="n">
-        <v>6669097.783335357</v>
+        <v>6669228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,19 +1066,9 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73025448</v>
+        <v>73025441</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586025.1189699546</v>
+        <v>585751</v>
       </c>
       <c r="R6" t="n">
-        <v>6669215.773156391</v>
+        <v>6668975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,19 +1168,9 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,15 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73025447</v>
+        <v>73025445</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586010.0451036422</v>
+        <v>585943</v>
       </c>
       <c r="R7" t="n">
-        <v>6669198.981279041</v>
+        <v>6669098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,19 +1270,9 @@
           <t>2018-09-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,6 +1296,312 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73025447</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SV Svedbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>586010</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6669199</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73025448</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SV Svedbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>586025</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6669216</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>73025450</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SV Svedbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>586057</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6669274</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3930-2026 artfynd.xlsx
+++ b/artfynd/A 3930-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025451</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025446</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025439</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025441</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025445</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025447</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,8 +1647,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025450</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>